--- a/data/trans_orig/P59A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P59A-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2007</t>
+          <t>Población según si viven actualmente en pareja en 2007 (tasa de respuesta: 98,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34179</t>
+          <t>34724</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35379</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34999</t>
+          <t>36207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62732</t>
+          <t>62938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275242</t>
+          <t>274697</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293579</t>
+          <t>293569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>469278</t>
+          <t>469241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>489318</t>
+          <t>488592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>751346</t>
+          <t>751140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>779079</t>
+          <t>777871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88764</t>
+          <t>90208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130919</t>
+          <t>129305</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63439</t>
+          <t>62750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96962</t>
+          <t>97435</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163322</t>
+          <t>162887</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>213908</t>
+          <t>215696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>617357</t>
+          <t>618971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>659512</t>
+          <t>658068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556428</t>
+          <t>555955</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>589951</t>
+          <t>590640</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1187758</t>
+          <t>1185970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1238344</t>
+          <t>1238779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32866</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55940</t>
+          <t>57371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28284</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51364</t>
+          <t>51163</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67089</t>
+          <t>67313</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101454</t>
+          <t>101901</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174614</t>
+          <t>173183</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>197688</t>
+          <t>196599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172853</t>
+          <t>173054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>195933</t>
+          <t>196014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>353317</t>
+          <t>352870</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>387682</t>
+          <t>387458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>151556</t>
+          <t>152374</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204574</t>
+          <t>203455</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118904</t>
+          <t>118514</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164076</t>
+          <t>167653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>281649</t>
+          <t>284463</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>352236</t>
+          <t>353780</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1083678</t>
+          <t>1084797</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1136696</t>
+          <t>1135878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1218187</t>
+          <t>1214610</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1263359</t>
+          <t>1263749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2318279</t>
+          <t>2316735</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2388866</t>
+          <t>2386052</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2012</t>
+          <t>Población según si viven actualmente en pareja en 2012 (tasa de respuesta: 97,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25242</t>
+          <t>24519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>46723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23787</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48848</t>
+          <t>47936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52550</t>
+          <t>54654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87266</t>
+          <t>85882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257620</t>
+          <t>257792</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279273</t>
+          <t>279996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>445403</t>
+          <t>446315</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>470464</t>
+          <t>470524</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>711500</t>
+          <t>712884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>746216</t>
+          <t>744112</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115120</t>
+          <t>113411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>160122</t>
+          <t>159934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104813</t>
+          <t>106073</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146711</t>
+          <t>149002</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>230061</t>
+          <t>232061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>292717</t>
+          <t>294979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>701205</t>
+          <t>701393</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>746207</t>
+          <t>747916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>581291</t>
+          <t>579000</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>623189</t>
+          <t>621929</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1296612</t>
+          <t>1294350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1359268</t>
+          <t>1357268</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,4%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29565</t>
+          <t>29846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55570</t>
+          <t>55352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30771</t>
+          <t>30543</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>55595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67817</t>
+          <t>67637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104174</t>
+          <t>103445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>158256</t>
+          <t>158474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>184261</t>
+          <t>183980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140019</t>
+          <t>141856</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166680</t>
+          <t>166908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307103</t>
+          <t>307832</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>343460</t>
+          <t>343640</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>187770</t>
+          <t>185434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242377</t>
+          <t>240801</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>177407</t>
+          <t>176761</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>234163</t>
+          <t>233170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>373897</t>
+          <t>374383</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>456866</t>
+          <t>454747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1137290</t>
+          <t>1138866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1191897</t>
+          <t>1194233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1185541</t>
+          <t>1186534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1242297</t>
+          <t>1242943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2342506</t>
+          <t>2344625</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2425475</t>
+          <t>2424989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2016</t>
+          <t>Población según si viven actualmente en pareja en 2016 (tasa de respuesta: 97,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>16380</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35932</t>
+          <t>35311</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16211</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37567</t>
+          <t>36155</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63331</t>
+          <t>61953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229849</t>
+          <t>230470</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249344</t>
+          <t>249401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>368278</t>
+          <t>369690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389634</t>
+          <t>390193</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>608295</t>
+          <t>609673</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>636022</t>
+          <t>635849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>153807</t>
+          <t>149311</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>202550</t>
+          <t>198152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132801</t>
+          <t>134115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178024</t>
+          <t>177185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300411</t>
+          <t>296197</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>364837</t>
+          <t>364180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>734992</t>
+          <t>739390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>783735</t>
+          <t>788231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>741519</t>
+          <t>742358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>786742</t>
+          <t>785428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1492248</t>
+          <t>1492905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1556674</t>
+          <t>1560888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40812</t>
+          <t>40262</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68349</t>
+          <t>67385</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>34352</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>59391</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83747</t>
+          <t>82388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122248</t>
+          <t>119993</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>180139</t>
+          <t>181103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>207676</t>
+          <t>208226</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>200951</t>
+          <t>199902</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>225375</t>
+          <t>224941</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>385533</t>
+          <t>387788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>424034</t>
+          <t>425393</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,77%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223046</t>
+          <t>223686</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>285012</t>
+          <t>283670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>199292</t>
+          <t>195943</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>252336</t>
+          <t>249785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>437005</t>
+          <t>436242</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>521440</t>
+          <t>518646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1166799</t>
+          <t>1168141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1228765</t>
+          <t>1228125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1332345</t>
+          <t>1334896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1385389</t>
+          <t>1388738</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2515052</t>
+          <t>2517846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2599487</t>
+          <t>2600250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2023</t>
+          <t>Población según si viven actualmente en pareja en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35843</t>
+          <t>35713</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15435</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33932</t>
+          <t>34811</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33569</t>
+          <t>33940</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61064</t>
+          <t>61071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>194327</t>
+          <t>194457</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215200</t>
+          <t>215024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>376989</t>
+          <t>376110</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395486</t>
+          <t>395248</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>580027</t>
+          <t>580020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>607522</t>
+          <t>607151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>146245</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>214089</t>
+          <t>214511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106584</t>
+          <t>108722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>164853</t>
+          <t>166553</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>276334</t>
+          <t>276940</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>363533</t>
+          <t>360972</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>889555</t>
+          <t>889133</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>957399</t>
+          <t>954093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>840887</t>
+          <t>839187</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>899156</t>
+          <t>897018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1745851</t>
+          <t>1748412</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1833050</t>
+          <t>1832444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39590</t>
+          <t>41845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72511</t>
+          <t>71731</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53952</t>
+          <t>54572</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81368</t>
+          <t>82073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101292</t>
+          <t>101040</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142632</t>
+          <t>143252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>219511</t>
+          <t>220291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>252432</t>
+          <t>250177</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250205</t>
+          <t>249500</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277621</t>
+          <t>277001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>480964</t>
+          <t>480344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>522304</t>
+          <t>522556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223729</t>
+          <t>222946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>299709</t>
+          <t>298835</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>198021</t>
+          <t>195638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>263968</t>
+          <t>260499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>437024</t>
+          <t>435763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>536880</t>
+          <t>534167</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1326127</t>
+          <t>1327001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1402107</t>
+          <t>1402890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1484267</t>
+          <t>1487736</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1550214</t>
+          <t>1552597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2837191</t>
+          <t>2839904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2937047</t>
+          <t>2938308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P59A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P59A-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34724</t>
+          <t>35331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>35187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62938</t>
+          <t>63532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274697</t>
+          <t>274090</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293569</t>
+          <t>293755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>469241</t>
+          <t>469470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>488592</t>
+          <t>490134</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>751140</t>
+          <t>750546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>777871</t>
+          <t>778554</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90208</t>
+          <t>88983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129305</t>
+          <t>128484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62750</t>
+          <t>62758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97435</t>
+          <t>95441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>162887</t>
+          <t>159779</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>215696</t>
+          <t>213690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>618971</t>
+          <t>619792</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>658068</t>
+          <t>659293</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555955</t>
+          <t>557949</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>590640</t>
+          <t>590632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1185970</t>
+          <t>1187976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1238779</t>
+          <t>1241887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>32566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57371</t>
+          <t>58540</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51163</t>
+          <t>52632</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67313</t>
+          <t>66880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101901</t>
+          <t>100745</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173183</t>
+          <t>172014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>196599</t>
+          <t>197988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173054</t>
+          <t>171585</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>196014</t>
+          <t>195460</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>352870</t>
+          <t>354026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>387458</t>
+          <t>387891</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>152374</t>
+          <t>152328</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>203455</t>
+          <t>203813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118514</t>
+          <t>119166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167653</t>
+          <t>166694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>284463</t>
+          <t>284529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>353780</t>
+          <t>357341</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1084797</t>
+          <t>1084439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1135878</t>
+          <t>1135924</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1214610</t>
+          <t>1215569</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1263749</t>
+          <t>1263097</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2316735</t>
+          <t>2313174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2386052</t>
+          <t>2385986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24519</t>
+          <t>24814</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46723</t>
+          <t>46878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47936</t>
+          <t>47702</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54654</t>
+          <t>54526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85882</t>
+          <t>85135</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257792</t>
+          <t>257637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279996</t>
+          <t>279701</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>446315</t>
+          <t>446549</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>470524</t>
+          <t>470584</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712884</t>
+          <t>713631</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744112</t>
+          <t>744240</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113411</t>
+          <t>112672</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159934</t>
+          <t>159763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106073</t>
+          <t>107705</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149002</t>
+          <t>147552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232061</t>
+          <t>228737</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>294979</t>
+          <t>292175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>701393</t>
+          <t>701564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>747916</t>
+          <t>748655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>579000</t>
+          <t>580450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>621929</t>
+          <t>620297</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1294350</t>
+          <t>1297154</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1357268</t>
+          <t>1360592</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,61%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29846</t>
+          <t>30350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55352</t>
+          <t>55112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>31582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55595</t>
+          <t>56600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67637</t>
+          <t>67651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103445</t>
+          <t>102799</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>158474</t>
+          <t>158714</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183980</t>
+          <t>183476</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141856</t>
+          <t>140851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166908</t>
+          <t>165869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307832</t>
+          <t>308478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>343640</t>
+          <t>343626</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>185434</t>
+          <t>186033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>240801</t>
+          <t>241360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>176761</t>
+          <t>176003</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>233170</t>
+          <t>232477</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>374383</t>
+          <t>377113</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>454747</t>
+          <t>454723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1138866</t>
+          <t>1138307</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1194233</t>
+          <t>1193634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1186534</t>
+          <t>1187227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1242943</t>
+          <t>1243701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2344625</t>
+          <t>2344649</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2424989</t>
+          <t>2422259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,53%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35311</t>
+          <t>35048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36155</t>
+          <t>35174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>35051</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61953</t>
+          <t>62223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>230470</t>
+          <t>230733</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249401</t>
+          <t>249661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>369690</t>
+          <t>370671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>390193</t>
+          <t>389902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>609673</t>
+          <t>609403</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>635849</t>
+          <t>636575</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>149311</t>
+          <t>150207</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>198152</t>
+          <t>201684</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134115</t>
+          <t>132516</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177185</t>
+          <t>176836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>296197</t>
+          <t>298520</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>364180</t>
+          <t>364915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>739390</t>
+          <t>735858</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>788231</t>
+          <t>787335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>742358</t>
+          <t>742707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>785428</t>
+          <t>787027</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1492905</t>
+          <t>1492170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1560888</t>
+          <t>1558565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,93%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40262</t>
+          <t>42114</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67385</t>
+          <t>68567</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34352</t>
+          <t>34263</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59391</t>
+          <t>58622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82388</t>
+          <t>80413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119993</t>
+          <t>118304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181103</t>
+          <t>179921</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>208226</t>
+          <t>206374</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>199902</t>
+          <t>200671</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>224941</t>
+          <t>225030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>387788</t>
+          <t>389477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>425393</t>
+          <t>427368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223686</t>
+          <t>224680</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>283670</t>
+          <t>284586</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195943</t>
+          <t>200525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>249785</t>
+          <t>254476</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,47 +5018,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>16,06%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>478404</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>439203</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>517434</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>15,76%</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>478404</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>436242</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>518646</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>15,76%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1168141</t>
+          <t>1167225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1228125</t>
+          <t>1227131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1334896</t>
+          <t>1330205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1388738</t>
+          <t>1384156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,47 +5131,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>83,94%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>87,35%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2558088</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2519058</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2597289</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>84,24%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>87,64%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2558088</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>2517846</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2600250</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>84,24%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23190</t>
+          <t>24687</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>14083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>37123</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23172</t>
+          <t>23156</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34811</t>
+          <t>34002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46361</t>
+          <t>47843</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33940</t>
+          <t>34806</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61071</t>
+          <t>63517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>206980</t>
+          <t>232502</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>194457</t>
+          <t>220066</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215024</t>
+          <t>243106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>387749</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>376110</t>
+          <t>407613</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395248</t>
+          <t>425784</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>594730</t>
+          <t>650960</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>580020</t>
+          <t>635286</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>607151</t>
+          <t>663997</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>230170</t>
+          <t>257189</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>230170</t>
+          <t>257189</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230170</t>
+          <t>257189</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>410921</t>
+          <t>441615</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>410921</t>
+          <t>441615</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>410921</t>
+          <t>441615</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>641091</t>
+          <t>698803</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>641091</t>
+          <t>698803</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>641091</t>
+          <t>698803</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>180144</t>
+          <t>200066</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>149551</t>
+          <t>170169</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>214511</t>
+          <t>236126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>138938</t>
+          <t>160788</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108722</t>
+          <t>135906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>166553</t>
+          <t>184737</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>319082</t>
+          <t>360854</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>276940</t>
+          <t>322021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>360972</t>
+          <t>402775</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>923500</t>
+          <t>971865</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>889133</t>
+          <t>935805</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>954093</t>
+          <t>1001762</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>866802</t>
+          <t>901277</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>839187</t>
+          <t>877328</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>897018</t>
+          <t>926159</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1790302</t>
+          <t>1873143</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1748412</t>
+          <t>1831222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1832444</t>
+          <t>1911976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1103644</t>
+          <t>1171931</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1103644</t>
+          <t>1171931</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1103644</t>
+          <t>1171931</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1005740</t>
+          <t>1062065</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1005740</t>
+          <t>1062065</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1005740</t>
+          <t>1062065</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2109384</t>
+          <t>2233997</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2109384</t>
+          <t>2233997</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2109384</t>
+          <t>2233997</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>55172</t>
+          <t>60445</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41845</t>
+          <t>46709</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71731</t>
+          <t>77897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66889</t>
+          <t>73743</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54572</t>
+          <t>59593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82073</t>
+          <t>88504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>122060</t>
+          <t>134188</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101040</t>
+          <t>113325</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143252</t>
+          <t>155188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>236850</t>
+          <t>253746</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>220291</t>
+          <t>236294</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>250177</t>
+          <t>267482</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>264684</t>
+          <t>289660</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249500</t>
+          <t>274899</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277001</t>
+          <t>303810</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>501536</t>
+          <t>543406</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>480344</t>
+          <t>522406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>522556</t>
+          <t>564269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>292022</t>
+          <t>314191</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>292022</t>
+          <t>314191</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>292022</t>
+          <t>314191</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>331573</t>
+          <t>363403</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>331573</t>
+          <t>363403</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>331573</t>
+          <t>363403</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>623596</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>623596</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>623596</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>258506</t>
+          <t>285198</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>222946</t>
+          <t>247448</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>298835</t>
+          <t>324797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>228998</t>
+          <t>257687</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195638</t>
+          <t>231172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260499</t>
+          <t>289584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>487504</t>
+          <t>542885</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>435763</t>
+          <t>494763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>534167</t>
+          <t>589512</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1367330</t>
+          <t>1458113</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1327001</t>
+          <t>1418514</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1402890</t>
+          <t>1495863</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1519237</t>
+          <t>1609395</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1487736</t>
+          <t>1577498</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1552597</t>
+          <t>1635910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2886567</t>
+          <t>3067509</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2839904</t>
+          <t>3020882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2938308</t>
+          <t>3115631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1625836</t>
+          <t>1743311</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1625836</t>
+          <t>1743311</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1625836</t>
+          <t>1743311</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1748235</t>
+          <t>1867082</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1748235</t>
+          <t>1867082</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1748235</t>
+          <t>1867082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3374071</t>
+          <t>3610394</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3374071</t>
+          <t>3610394</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3374071</t>
+          <t>3610394</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
